--- a/artfynd/A 47706-2025 artfynd.xlsx
+++ b/artfynd/A 47706-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>132408141</v>
       </c>
       <c r="B2" t="n">
-        <v>79315</v>
+        <v>79317</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>132408149</v>
       </c>
       <c r="B3" t="n">
-        <v>78322</v>
+        <v>78324</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>132408147</v>
       </c>
       <c r="B4" t="n">
-        <v>79934</v>
+        <v>79936</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>132408143</v>
       </c>
       <c r="B5" t="n">
-        <v>79315</v>
+        <v>79317</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1106,7 +1106,7 @@
         <v>132408134</v>
       </c>
       <c r="B6" t="n">
-        <v>58320</v>
+        <v>58322</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1437,7 +1437,7 @@
         <v>132408140</v>
       </c>
       <c r="B9" t="n">
-        <v>79315</v>
+        <v>79317</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1772,7 +1772,7 @@
         <v>132408135</v>
       </c>
       <c r="B12" t="n">
-        <v>80456</v>
+        <v>80458</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1879,7 +1879,7 @@
         <v>132408131</v>
       </c>
       <c r="B13" t="n">
-        <v>79315</v>
+        <v>79317</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1986,7 +1986,7 @@
         <v>132408150</v>
       </c>
       <c r="B14" t="n">
-        <v>79315</v>
+        <v>79317</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2093,7 +2093,7 @@
         <v>132408132</v>
       </c>
       <c r="B15" t="n">
-        <v>79315</v>
+        <v>79317</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2197,10 +2197,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>132408145</v>
+        <v>132408152</v>
       </c>
       <c r="B16" t="n">
-        <v>57948</v>
+        <v>91912</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2208,34 +2208,33 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Lars-Larsbäcken, Ås lm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>668763</v>
+        <v>668538</v>
       </c>
       <c r="R16" t="n">
-        <v>7104108</v>
+        <v>7104421</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2267,7 +2266,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2277,12 +2276,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:37</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>färska ringhack</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2291,6 +2285,7 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2309,10 +2304,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>132408152</v>
+        <v>132408145</v>
       </c>
       <c r="B17" t="n">
-        <v>91909</v>
+        <v>57948</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2320,33 +2315,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Lars-Larsbäcken, Ås lm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>668538</v>
+        <v>668763</v>
       </c>
       <c r="R17" t="n">
-        <v>7104421</v>
+        <v>7104108</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2378,7 +2374,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2388,7 +2384,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>14:37</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>färska ringhack</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2397,7 +2398,6 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2419,7 +2419,7 @@
         <v>132408151</v>
       </c>
       <c r="B18" t="n">
-        <v>79315</v>
+        <v>79317</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2523,10 +2523,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>132408153</v>
+        <v>132408144</v>
       </c>
       <c r="B19" t="n">
-        <v>57945</v>
+        <v>57948</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2534,16 +2534,16 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2558,10 +2558,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>668535</v>
+        <v>668808</v>
       </c>
       <c r="R19" t="n">
-        <v>7104418</v>
+        <v>7104046</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2593,7 +2593,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>födosök</t>
+          <t>färskt ringhack</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2635,10 +2635,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>132408144</v>
+        <v>132408153</v>
       </c>
       <c r="B20" t="n">
-        <v>57948</v>
+        <v>57945</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2646,16 +2646,16 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2670,10 +2670,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>668808</v>
+        <v>668535</v>
       </c>
       <c r="R20" t="n">
-        <v>7104046</v>
+        <v>7104418</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2705,7 +2705,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>färskt ringhack</t>
+          <t>födosök</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2750,7 +2750,7 @@
         <v>132408146</v>
       </c>
       <c r="B21" t="n">
-        <v>79315</v>
+        <v>79317</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2857,7 +2857,7 @@
         <v>132408148</v>
       </c>
       <c r="B22" t="n">
-        <v>79072</v>
+        <v>79074</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 47706-2025 artfynd.xlsx
+++ b/artfynd/A 47706-2025 artfynd.xlsx
@@ -2523,10 +2523,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>132408144</v>
+        <v>132408153</v>
       </c>
       <c r="B19" t="n">
-        <v>57948</v>
+        <v>57945</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2534,16 +2534,16 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2558,10 +2558,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>668808</v>
+        <v>668535</v>
       </c>
       <c r="R19" t="n">
-        <v>7104046</v>
+        <v>7104418</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2593,7 +2593,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>färskt ringhack</t>
+          <t>födosök</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2635,10 +2635,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>132408153</v>
+        <v>132408144</v>
       </c>
       <c r="B20" t="n">
-        <v>57945</v>
+        <v>57948</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2646,16 +2646,16 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2670,10 +2670,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>668535</v>
+        <v>668808</v>
       </c>
       <c r="R20" t="n">
-        <v>7104418</v>
+        <v>7104046</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2705,7 +2705,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>födosök</t>
+          <t>färskt ringhack</t>
         </is>
       </c>
       <c r="AD20" t="b">

--- a/artfynd/A 47706-2025 artfynd.xlsx
+++ b/artfynd/A 47706-2025 artfynd.xlsx
@@ -1657,10 +1657,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>132408139</v>
+        <v>132408131</v>
       </c>
       <c r="B11" t="n">
-        <v>57945</v>
+        <v>79317</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1668,21 +1668,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1692,10 +1692,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>668561</v>
+        <v>669115</v>
       </c>
       <c r="R11" t="n">
-        <v>7104360</v>
+        <v>7103755</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1722,27 +1722,22 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
+          <t>2026-04-05</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>08:39</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
+          <t>2026-04-05</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:13</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>födosök</t>
+          <t>08:39</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1876,10 +1871,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>132408131</v>
+        <v>132408139</v>
       </c>
       <c r="B13" t="n">
-        <v>79317</v>
+        <v>57945</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1887,21 +1882,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1911,10 +1906,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>669115</v>
+        <v>668561</v>
       </c>
       <c r="R13" t="n">
-        <v>7103755</v>
+        <v>7104360</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1941,22 +1936,27 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2026-04-05</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>08:39</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2026-04-05</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>08:39</t>
+          <t>15:13</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>födosök</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2523,10 +2523,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>132408153</v>
+        <v>132408144</v>
       </c>
       <c r="B19" t="n">
-        <v>57945</v>
+        <v>57948</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2534,16 +2534,16 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2558,10 +2558,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>668535</v>
+        <v>668808</v>
       </c>
       <c r="R19" t="n">
-        <v>7104418</v>
+        <v>7104046</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2593,7 +2593,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>födosök</t>
+          <t>färskt ringhack</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2635,10 +2635,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>132408144</v>
+        <v>132408153</v>
       </c>
       <c r="B20" t="n">
-        <v>57948</v>
+        <v>57945</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2646,16 +2646,16 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2670,10 +2670,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>668808</v>
+        <v>668535</v>
       </c>
       <c r="R20" t="n">
-        <v>7104046</v>
+        <v>7104418</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2705,7 +2705,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>färskt ringhack</t>
+          <t>födosök</t>
         </is>
       </c>
       <c r="AD20" t="b">

--- a/artfynd/A 47706-2025 artfynd.xlsx
+++ b/artfynd/A 47706-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>132408141</v>
       </c>
       <c r="B2" t="n">
-        <v>79317</v>
+        <v>79319</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>132408149</v>
       </c>
       <c r="B3" t="n">
-        <v>78324</v>
+        <v>78326</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>132408147</v>
       </c>
       <c r="B4" t="n">
-        <v>79936</v>
+        <v>79938</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>132408143</v>
       </c>
       <c r="B5" t="n">
-        <v>79317</v>
+        <v>79319</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1106,7 +1106,7 @@
         <v>132408134</v>
       </c>
       <c r="B6" t="n">
-        <v>58322</v>
+        <v>58323</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>132408129</v>
       </c>
       <c r="B7" t="n">
-        <v>57948</v>
+        <v>57949</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1325,7 +1325,7 @@
         <v>132408142</v>
       </c>
       <c r="B8" t="n">
-        <v>57945</v>
+        <v>57946</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1437,7 +1437,7 @@
         <v>132408140</v>
       </c>
       <c r="B9" t="n">
-        <v>79317</v>
+        <v>79319</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1544,7 +1544,7 @@
         <v>132408133</v>
       </c>
       <c r="B10" t="n">
-        <v>57948</v>
+        <v>57949</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1660,7 +1660,7 @@
         <v>132408131</v>
       </c>
       <c r="B11" t="n">
-        <v>79317</v>
+        <v>79319</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1767,7 +1767,7 @@
         <v>132408135</v>
       </c>
       <c r="B12" t="n">
-        <v>80458</v>
+        <v>80460</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1874,7 +1874,7 @@
         <v>132408139</v>
       </c>
       <c r="B13" t="n">
-        <v>57945</v>
+        <v>57946</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1986,7 +1986,7 @@
         <v>132408150</v>
       </c>
       <c r="B14" t="n">
-        <v>79317</v>
+        <v>79319</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2093,7 +2093,7 @@
         <v>132408132</v>
       </c>
       <c r="B15" t="n">
-        <v>79317</v>
+        <v>79319</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2200,7 +2200,7 @@
         <v>132408152</v>
       </c>
       <c r="B16" t="n">
-        <v>91912</v>
+        <v>91918</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2307,7 +2307,7 @@
         <v>132408145</v>
       </c>
       <c r="B17" t="n">
-        <v>57948</v>
+        <v>57949</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2419,7 +2419,7 @@
         <v>132408151</v>
       </c>
       <c r="B18" t="n">
-        <v>79317</v>
+        <v>79319</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2526,7 +2526,7 @@
         <v>132408144</v>
       </c>
       <c r="B19" t="n">
-        <v>57948</v>
+        <v>57949</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2638,7 +2638,7 @@
         <v>132408153</v>
       </c>
       <c r="B20" t="n">
-        <v>57945</v>
+        <v>57946</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2750,7 +2750,7 @@
         <v>132408146</v>
       </c>
       <c r="B21" t="n">
-        <v>79317</v>
+        <v>79319</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2857,7 +2857,7 @@
         <v>132408148</v>
       </c>
       <c r="B22" t="n">
-        <v>79074</v>
+        <v>79076</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 47706-2025 artfynd.xlsx
+++ b/artfynd/A 47706-2025 artfynd.xlsx
@@ -1434,10 +1434,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>132408140</v>
+        <v>132408133</v>
       </c>
       <c r="B9" t="n">
-        <v>79319</v>
+        <v>57949</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1445,34 +1445,38 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Lars-Larsbäcken, Ås lm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>668922</v>
+        <v>669141</v>
       </c>
       <c r="R9" t="n">
-        <v>7104021</v>
+        <v>7103773</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1499,22 +1503,27 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
+          <t>2026-04-05</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>08:35</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
+          <t>2026-04-05</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>08:35</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>äldre ringhack</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1541,10 +1550,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>132408133</v>
+        <v>132408140</v>
       </c>
       <c r="B10" t="n">
-        <v>57949</v>
+        <v>79319</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1552,38 +1561,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Lars-Larsbäcken, Ås lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>669141</v>
+        <v>668922</v>
       </c>
       <c r="R10" t="n">
-        <v>7103773</v>
+        <v>7104021</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1610,27 +1615,22 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2026-04-05</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>08:35</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-04-05</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>08:35</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>äldre ringhack</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -2197,10 +2197,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>132408152</v>
+        <v>132408145</v>
       </c>
       <c r="B16" t="n">
-        <v>91918</v>
+        <v>57949</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2208,33 +2208,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Lars-Larsbäcken, Ås lm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>668538</v>
+        <v>668763</v>
       </c>
       <c r="R16" t="n">
-        <v>7104421</v>
+        <v>7104108</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2266,7 +2267,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2276,7 +2277,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>14:37</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>färska ringhack</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2285,7 +2291,6 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2304,10 +2309,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>132408145</v>
+        <v>132408152</v>
       </c>
       <c r="B17" t="n">
-        <v>57949</v>
+        <v>91918</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2315,34 +2320,33 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Lars-Larsbäcken, Ås lm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>668763</v>
+        <v>668538</v>
       </c>
       <c r="R17" t="n">
-        <v>7104108</v>
+        <v>7104421</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2374,7 +2378,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2384,12 +2388,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>14:37</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>färska ringhack</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2398,6 +2397,7 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2523,10 +2523,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>132408144</v>
+        <v>132408153</v>
       </c>
       <c r="B19" t="n">
-        <v>57949</v>
+        <v>57946</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2534,16 +2534,16 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2558,10 +2558,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>668808</v>
+        <v>668535</v>
       </c>
       <c r="R19" t="n">
-        <v>7104046</v>
+        <v>7104418</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2593,7 +2593,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>färskt ringhack</t>
+          <t>födosök</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2635,10 +2635,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>132408153</v>
+        <v>132408144</v>
       </c>
       <c r="B20" t="n">
-        <v>57946</v>
+        <v>57949</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2646,16 +2646,16 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2670,10 +2670,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>668535</v>
+        <v>668808</v>
       </c>
       <c r="R20" t="n">
-        <v>7104418</v>
+        <v>7104046</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2705,7 +2705,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>födosök</t>
+          <t>färskt ringhack</t>
         </is>
       </c>
       <c r="AD20" t="b">

--- a/artfynd/A 47706-2025 artfynd.xlsx
+++ b/artfynd/A 47706-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>132408141</v>
       </c>
       <c r="B2" t="n">
-        <v>79319</v>
+        <v>79327</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>132408149</v>
       </c>
       <c r="B3" t="n">
-        <v>78326</v>
+        <v>78334</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>132408147</v>
       </c>
       <c r="B4" t="n">
-        <v>79938</v>
+        <v>79946</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>132408143</v>
       </c>
       <c r="B5" t="n">
-        <v>79319</v>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1106,7 +1106,7 @@
         <v>132408134</v>
       </c>
       <c r="B6" t="n">
-        <v>58323</v>
+        <v>58327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>132408129</v>
       </c>
       <c r="B7" t="n">
-        <v>57949</v>
+        <v>57953</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1325,7 +1325,7 @@
         <v>132408142</v>
       </c>
       <c r="B8" t="n">
-        <v>57946</v>
+        <v>57950</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1434,10 +1434,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>132408133</v>
+        <v>132408140</v>
       </c>
       <c r="B9" t="n">
-        <v>57949</v>
+        <v>79327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1445,38 +1445,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Lars-Larsbäcken, Ås lm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>669141</v>
+        <v>668922</v>
       </c>
       <c r="R9" t="n">
-        <v>7103773</v>
+        <v>7104021</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1503,27 +1499,22 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2026-04-05</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>08:35</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-04-05</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>08:35</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>äldre ringhack</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1550,10 +1541,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>132408140</v>
+        <v>132408133</v>
       </c>
       <c r="B10" t="n">
-        <v>79319</v>
+        <v>57953</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1561,34 +1552,38 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Lars-Larsbäcken, Ås lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>668922</v>
+        <v>669141</v>
       </c>
       <c r="R10" t="n">
-        <v>7104021</v>
+        <v>7103773</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1615,22 +1610,27 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
+          <t>2026-04-05</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>08:35</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
+          <t>2026-04-05</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>08:35</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>äldre ringhack</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1657,10 +1657,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>132408131</v>
+        <v>132408139</v>
       </c>
       <c r="B11" t="n">
-        <v>79319</v>
+        <v>57950</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1668,21 +1668,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1692,10 +1692,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>669115</v>
+        <v>668561</v>
       </c>
       <c r="R11" t="n">
-        <v>7103755</v>
+        <v>7104360</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1722,22 +1722,27 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2026-04-05</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>08:39</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-04-05</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>08:39</t>
+          <t>15:13</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>födosök</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1764,32 +1769,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>132408135</v>
+        <v>132408131</v>
       </c>
       <c r="B12" t="n">
-        <v>80460</v>
+        <v>79327</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1799,10 +1804,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>669167</v>
+        <v>669115</v>
       </c>
       <c r="R12" t="n">
-        <v>7103750</v>
+        <v>7103755</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1834,7 +1839,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>08:39</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1844,7 +1849,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>08:39</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1871,32 +1876,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>132408139</v>
+        <v>132408135</v>
       </c>
       <c r="B13" t="n">
-        <v>57946</v>
+        <v>80468</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>6464</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1906,10 +1911,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>668561</v>
+        <v>669167</v>
       </c>
       <c r="R13" t="n">
-        <v>7104360</v>
+        <v>7103750</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1936,27 +1941,22 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
+          <t>2026-04-05</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
+          <t>2026-04-05</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:13</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>födosök</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1986,7 +1986,7 @@
         <v>132408150</v>
       </c>
       <c r="B14" t="n">
-        <v>79319</v>
+        <v>79327</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2093,7 +2093,7 @@
         <v>132408132</v>
       </c>
       <c r="B15" t="n">
-        <v>79319</v>
+        <v>79327</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2200,7 +2200,7 @@
         <v>132408145</v>
       </c>
       <c r="B16" t="n">
-        <v>57949</v>
+        <v>57953</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2312,7 +2312,7 @@
         <v>132408152</v>
       </c>
       <c r="B17" t="n">
-        <v>91918</v>
+        <v>91928</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2419,7 +2419,7 @@
         <v>132408151</v>
       </c>
       <c r="B18" t="n">
-        <v>79319</v>
+        <v>79327</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2523,10 +2523,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>132408153</v>
+        <v>132408144</v>
       </c>
       <c r="B19" t="n">
-        <v>57946</v>
+        <v>57953</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2534,16 +2534,16 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2558,10 +2558,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>668535</v>
+        <v>668808</v>
       </c>
       <c r="R19" t="n">
-        <v>7104418</v>
+        <v>7104046</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2593,7 +2593,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>födosök</t>
+          <t>färskt ringhack</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2635,10 +2635,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>132408144</v>
+        <v>132408153</v>
       </c>
       <c r="B20" t="n">
-        <v>57949</v>
+        <v>57950</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2646,16 +2646,16 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2670,10 +2670,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>668808</v>
+        <v>668535</v>
       </c>
       <c r="R20" t="n">
-        <v>7104046</v>
+        <v>7104418</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2705,7 +2705,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>färskt ringhack</t>
+          <t>födosök</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2750,7 +2750,7 @@
         <v>132408146</v>
       </c>
       <c r="B21" t="n">
-        <v>79319</v>
+        <v>79327</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2857,7 +2857,7 @@
         <v>132408148</v>
       </c>
       <c r="B22" t="n">
-        <v>79076</v>
+        <v>79084</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 47706-2025 artfynd.xlsx
+++ b/artfynd/A 47706-2025 artfynd.xlsx
@@ -1657,10 +1657,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>132408139</v>
+        <v>132408131</v>
       </c>
       <c r="B11" t="n">
-        <v>57950</v>
+        <v>79327</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1668,21 +1668,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1692,10 +1692,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>668561</v>
+        <v>669115</v>
       </c>
       <c r="R11" t="n">
-        <v>7104360</v>
+        <v>7103755</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1722,27 +1722,22 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
+          <t>2026-04-05</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>08:39</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
+          <t>2026-04-05</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:13</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>födosök</t>
+          <t>08:39</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1769,10 +1764,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>132408131</v>
+        <v>132408139</v>
       </c>
       <c r="B12" t="n">
-        <v>79327</v>
+        <v>57950</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1780,21 +1775,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1804,10 +1799,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>669115</v>
+        <v>668561</v>
       </c>
       <c r="R12" t="n">
-        <v>7103755</v>
+        <v>7104360</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1834,22 +1829,27 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2026-04-05</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>08:39</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2026-04-05</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>08:39</t>
+          <t>15:13</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>födosök</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2197,10 +2197,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>132408145</v>
+        <v>132408152</v>
       </c>
       <c r="B16" t="n">
-        <v>57953</v>
+        <v>91929</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2208,34 +2208,33 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Lars-Larsbäcken, Ås lm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>668763</v>
+        <v>668538</v>
       </c>
       <c r="R16" t="n">
-        <v>7104108</v>
+        <v>7104421</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2267,7 +2266,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2277,12 +2276,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:37</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>färska ringhack</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2291,6 +2285,7 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2309,10 +2304,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>132408152</v>
+        <v>132408145</v>
       </c>
       <c r="B17" t="n">
-        <v>91928</v>
+        <v>57953</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2320,33 +2315,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Lars-Larsbäcken, Ås lm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>668538</v>
+        <v>668763</v>
       </c>
       <c r="R17" t="n">
-        <v>7104421</v>
+        <v>7104108</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2378,7 +2374,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2388,7 +2384,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>14:37</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>färska ringhack</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2397,7 +2398,6 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2523,10 +2523,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>132408144</v>
+        <v>132408153</v>
       </c>
       <c r="B19" t="n">
-        <v>57953</v>
+        <v>57950</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2534,16 +2534,16 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2558,10 +2558,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>668808</v>
+        <v>668535</v>
       </c>
       <c r="R19" t="n">
-        <v>7104046</v>
+        <v>7104418</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2593,7 +2593,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>färskt ringhack</t>
+          <t>födosök</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2635,10 +2635,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>132408153</v>
+        <v>132408144</v>
       </c>
       <c r="B20" t="n">
-        <v>57950</v>
+        <v>57953</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2646,16 +2646,16 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2670,10 +2670,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>668535</v>
+        <v>668808</v>
       </c>
       <c r="R20" t="n">
-        <v>7104418</v>
+        <v>7104046</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2705,7 +2705,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>födosök</t>
+          <t>färskt ringhack</t>
         </is>
       </c>
       <c r="AD20" t="b">

--- a/artfynd/A 47706-2025 artfynd.xlsx
+++ b/artfynd/A 47706-2025 artfynd.xlsx
@@ -1434,10 +1434,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>132408140</v>
+        <v>132408133</v>
       </c>
       <c r="B9" t="n">
-        <v>79327</v>
+        <v>57953</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1445,34 +1445,38 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Lars-Larsbäcken, Ås lm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>668922</v>
+        <v>669141</v>
       </c>
       <c r="R9" t="n">
-        <v>7104021</v>
+        <v>7103773</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1499,22 +1503,27 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
+          <t>2026-04-05</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>08:35</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
+          <t>2026-04-05</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>08:35</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>äldre ringhack</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1541,10 +1550,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>132408133</v>
+        <v>132408140</v>
       </c>
       <c r="B10" t="n">
-        <v>57953</v>
+        <v>79327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1552,38 +1561,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Lars-Larsbäcken, Ås lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>669141</v>
+        <v>668922</v>
       </c>
       <c r="R10" t="n">
-        <v>7103773</v>
+        <v>7104021</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1610,27 +1615,22 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2026-04-05</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>08:35</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-04-05</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>08:35</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>äldre ringhack</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1657,10 +1657,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>132408131</v>
+        <v>132408139</v>
       </c>
       <c r="B11" t="n">
-        <v>79327</v>
+        <v>57950</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1668,21 +1668,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1692,10 +1692,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>669115</v>
+        <v>668561</v>
       </c>
       <c r="R11" t="n">
-        <v>7103755</v>
+        <v>7104360</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1722,22 +1722,27 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2026-04-05</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>08:39</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-04-05</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>08:39</t>
+          <t>15:13</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>födosök</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1764,10 +1769,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>132408139</v>
+        <v>132408131</v>
       </c>
       <c r="B12" t="n">
-        <v>57950</v>
+        <v>79327</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1775,21 +1780,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1799,10 +1804,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>668561</v>
+        <v>669115</v>
       </c>
       <c r="R12" t="n">
-        <v>7104360</v>
+        <v>7103755</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1829,27 +1834,22 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
+          <t>2026-04-05</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>08:39</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
+          <t>2026-04-05</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:13</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>födosök</t>
+          <t>08:39</t>
         </is>
       </c>
       <c r="AD12" t="b">

--- a/artfynd/A 47706-2025 artfynd.xlsx
+++ b/artfynd/A 47706-2025 artfynd.xlsx
@@ -1657,10 +1657,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>132408139</v>
+        <v>132408131</v>
       </c>
       <c r="B11" t="n">
-        <v>57950</v>
+        <v>79327</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1668,21 +1668,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1692,10 +1692,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>668561</v>
+        <v>669115</v>
       </c>
       <c r="R11" t="n">
-        <v>7104360</v>
+        <v>7103755</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1722,27 +1722,22 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
+          <t>2026-04-05</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>08:39</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
+          <t>2026-04-05</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:13</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>födosök</t>
+          <t>08:39</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1769,32 +1764,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>132408131</v>
+        <v>132408135</v>
       </c>
       <c r="B12" t="n">
-        <v>79327</v>
+        <v>80468</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1804,10 +1799,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>669115</v>
+        <v>669167</v>
       </c>
       <c r="R12" t="n">
-        <v>7103755</v>
+        <v>7103750</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1839,7 +1834,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>08:39</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1849,7 +1844,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>08:39</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1876,32 +1871,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>132408135</v>
+        <v>132408139</v>
       </c>
       <c r="B13" t="n">
-        <v>80468</v>
+        <v>57950</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6464</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1911,10 +1906,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>669167</v>
+        <v>668561</v>
       </c>
       <c r="R13" t="n">
-        <v>7103750</v>
+        <v>7104360</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1941,22 +1936,27 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2026-04-05</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2026-04-05</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>15:13</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>födosök</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2523,10 +2523,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>132408153</v>
+        <v>132408144</v>
       </c>
       <c r="B19" t="n">
-        <v>57950</v>
+        <v>57953</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2534,16 +2534,16 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2558,10 +2558,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>668535</v>
+        <v>668808</v>
       </c>
       <c r="R19" t="n">
-        <v>7104418</v>
+        <v>7104046</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2593,7 +2593,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>födosök</t>
+          <t>färskt ringhack</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2635,10 +2635,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>132408144</v>
+        <v>132408153</v>
       </c>
       <c r="B20" t="n">
-        <v>57953</v>
+        <v>57950</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2646,16 +2646,16 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2670,10 +2670,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>668808</v>
+        <v>668535</v>
       </c>
       <c r="R20" t="n">
-        <v>7104046</v>
+        <v>7104418</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2705,7 +2705,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>färskt ringhack</t>
+          <t>födosök</t>
         </is>
       </c>
       <c r="AD20" t="b">

--- a/artfynd/A 47706-2025 artfynd.xlsx
+++ b/artfynd/A 47706-2025 artfynd.xlsx
@@ -1657,32 +1657,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>132408131</v>
+        <v>132408135</v>
       </c>
       <c r="B11" t="n">
-        <v>79327</v>
+        <v>80468</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1692,10 +1692,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>669115</v>
+        <v>669167</v>
       </c>
       <c r="R11" t="n">
-        <v>7103755</v>
+        <v>7103750</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1727,7 +1727,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>08:39</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1737,7 +1737,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>08:39</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1764,32 +1764,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>132408135</v>
+        <v>132408131</v>
       </c>
       <c r="B12" t="n">
-        <v>80468</v>
+        <v>79327</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1799,10 +1799,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>669167</v>
+        <v>669115</v>
       </c>
       <c r="R12" t="n">
-        <v>7103750</v>
+        <v>7103755</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1834,7 +1834,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>08:39</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1844,7 +1844,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>08:39</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2523,10 +2523,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>132408144</v>
+        <v>132408153</v>
       </c>
       <c r="B19" t="n">
-        <v>57953</v>
+        <v>57950</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2534,16 +2534,16 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2558,10 +2558,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>668808</v>
+        <v>668535</v>
       </c>
       <c r="R19" t="n">
-        <v>7104046</v>
+        <v>7104418</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2593,7 +2593,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>färskt ringhack</t>
+          <t>födosök</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2635,10 +2635,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>132408153</v>
+        <v>132408144</v>
       </c>
       <c r="B20" t="n">
-        <v>57950</v>
+        <v>57953</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2646,16 +2646,16 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2670,10 +2670,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>668535</v>
+        <v>668808</v>
       </c>
       <c r="R20" t="n">
-        <v>7104418</v>
+        <v>7104046</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2705,7 +2705,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>födosök</t>
+          <t>färskt ringhack</t>
         </is>
       </c>
       <c r="AD20" t="b">
